--- a/4_Editora/2024_06_Publicacoes_por_Editora_Privada.xlsx
+++ b/4_Editora/2024_06_Publicacoes_por_Editora_Privada.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
   <si>
     <t xml:space="preserve">Instituições</t>
   </si>
@@ -44,6 +44,9 @@
     <t xml:space="preserve">Total de Publicações</t>
   </si>
   <si>
+    <t xml:space="preserve">Acesso Aberto</t>
+  </si>
+  <si>
     <t xml:space="preserve">Universidade Católica Portuguesa</t>
   </si>
   <si>
@@ -63,7 +66,7 @@
     <t xml:space="preserve">Universidade do Porto</t>
   </si>
   <si>
-    <t xml:space="preserve">U Porto Press</t>
+    <t xml:space="preserve">U.Porto Press</t>
   </si>
   <si>
     <t xml:space="preserve">Universidade Fernando Pessoa</t>
@@ -92,7 +95,7 @@
 Autónoma de Lisboa</t>
   </si>
   <si>
-    <t xml:space="preserve">Serviços Editoriais da UAL (EDIUAL)</t>
+    <t xml:space="preserve">Serviços Editoriais da UAL (EdiUAL)</t>
   </si>
   <si>
     <t xml:space="preserve">2023-2026</t>
@@ -215,7 +218,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -234,6 +237,10 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -322,8 +329,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="27.25"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.38"/>
@@ -352,119 +359,125 @@
       <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="5" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="25.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="6" t="s">
+      <c r="A2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="B2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="6" t="n">
         <v>1998</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="5" t="n">
-        <v>58</v>
+      <c r="F2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>996</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>2002</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="5" t="n">
-        <v>2002</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>399</v>
+      <c r="G3" s="6" t="n">
+        <v>239</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>74</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="B4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="6" t="n">
         <v>1992</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="5" t="n">
+      <c r="D4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="25.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="6" t="s">
+      <c r="A5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="B5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="5" t="n">
+      <c r="D5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="6" t="n">
         <v>172</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="25.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="5" t="s">
+      <c r="A6" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="B6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="6" t="n">
         <v>1993</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="5" t="n">
+      <c r="D6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="6" t="n">
         <v>0</v>
       </c>
     </row>
